--- a/02_DIA_inicio_2026_analisis_assets/rbd_9738_colegio-parque-las-americas_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9738_colegio-parque-las-americas_nt2_rubricas.xlsx
@@ -1956,13 +1956,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50E534BF-666F-4E22-B6DC-9161BB41E2D8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D4E076A-EA75-4DC8-A727-0CE06587C425}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22995BB6-3C1E-4948-BF86-437408EA0E95}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{915BABF2-2682-4A19-9071-161610E6DB0B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09876D6B-7B15-4945-9220-1D14BAEB6F33}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2032DAC1-705E-4A13-95C8-F181F9866ABB}"/>
 </file>